--- a/DataTables/Datas/battle.encounter.xlsx
+++ b/DataTables/Datas/battle.encounter.xlsx
@@ -61,7 +61,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,13 +77,123 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F9F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF9EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F4FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF5F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7EFCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFE7F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E9E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F1F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -100,8 +210,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,48 +558,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="1">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="4">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="4">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="6">
         <v>5001</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>2001</v>
       </c>
     </row>

--- a/DataTables/Datas/battle.encounter.xlsx
+++ b/DataTables/Datas/battle.encounter.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51fdf121ba8c456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd7215dda84ce4050"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -392,6 +392,7 @@
     <x:col min="1" max="1" width="8.75" customWidth="1"/>
     <x:col min="2" max="2" width="9.5" customWidth="1"/>
     <x:col min="3" max="3" width="20.75" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -404,6 +405,9 @@
       <x:c r="C1" s="1" t="s">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="D1" t="str">
+        <x:v>phase_two_behavior_group_id</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="s">
@@ -415,11 +419,15 @@
       <x:c r="C2" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="D2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="D3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="s">
@@ -431,6 +439,9 @@
       <x:c r="C4" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Phase two behavior group ID; 0 means none</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="6">
@@ -438,6 +449,33 @@
       </x:c>
       <x:c r="C5" s="7" t="str">
         <x:v>2001,2002</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6"/>
+      <x:c r="B6" t="n">
+        <x:v>5101</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>2101</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7" t="n">
+        <x:v>5201</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>2201</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>6202</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
